--- a/other/babysitting_release_form.xlsx
+++ b/other/babysitting_release_form.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -927,6 +937,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>medical_conditions_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>medical_conditions_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>contact_preference_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>contact_preference_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
